--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120829824</v>
+        <v>120829791</v>
       </c>
       <c r="B14" t="n">
-        <v>98108</v>
+        <v>98118</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2266,17 +2266,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Det minsta antal jag sett !</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2297,6 +2297,133 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>56918206</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56435</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>540003</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6631018</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2016-02-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2016-02-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2052,59 +2052,58 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113141447</v>
+        <v>56918206</v>
       </c>
       <c r="B13" t="n">
-        <v>108510</v>
+        <v>56529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>100045</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Folkhögskolebäcken, väg bredvid (svinrot), Vstm</t>
+          <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2136,19 +2135,24 @@
           <t>Skinnskatteberg</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>U-Ski-0226</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2016-02-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2016-02-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,7 +2161,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2172,257 +2175,7 @@
           <t>Leif Johansson</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>120829791</v>
-      </c>
-      <c r="B14" t="n">
-        <v>98118</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>219875</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Platanthera chlorantha</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>540003</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6631018</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Skinnskatteberg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Skinnskatteberg</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Leif Johansson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Leif Johansson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>56918206</v>
-      </c>
-      <c r="B15" t="n">
-        <v>56529</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100045</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Sångsvan</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Cygnus cygnus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>540003</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6631018</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Skinnskatteberg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Skinnskatteberg</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2016-02-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2016-02-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Leif Johansson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Leif Johansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -1063,12 +1063,7 @@
         <v>59028932</v>
       </c>
       <c r="B5" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,10 +1106,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R5" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
         <v>59028932</v>
       </c>
       <c r="B5" t="n">
-        <v>58109</v>
+        <v>58135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -2050,12 +2050,7 @@
         <v>56918206</v>
       </c>
       <c r="B13" t="n">
-        <v>56529</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
         <v>59028932</v>
       </c>
       <c r="B5" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>56918206</v>
       </c>
       <c r="B13" t="n">
-        <v>56825</v>
+        <v>56827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
         <v>59028932</v>
       </c>
       <c r="B5" t="n">
-        <v>58137</v>
+        <v>58145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>56918206</v>
       </c>
       <c r="B13" t="n">
-        <v>56827</v>
+        <v>56835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
         <v>59028932</v>
       </c>
       <c r="B5" t="n">
-        <v>58145</v>
+        <v>58146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>56918206</v>
       </c>
       <c r="B13" t="n">
-        <v>56835</v>
+        <v>56836</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
         <v>59028932</v>
       </c>
       <c r="B5" t="n">
-        <v>58146</v>
+        <v>58147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2167,6 +2167,134 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131862902</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57743</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>540003</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6631018</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>samtidigt med den andra sparvugglan.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -2172,7 +2172,7 @@
         <v>131862902</v>
       </c>
       <c r="B14" t="n">
-        <v>57743</v>
+        <v>57745</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23016-2024 artfynd.xlsx
+++ b/artfynd/A 23016-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55694729</v>
+        <v>56918206</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R2" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +755,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2016-02-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2016-02-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55696483</v>
+        <v>69417872</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,49 +808,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R3" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,22 +873,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-06-23</t>
+          <t>2018-02-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-06-23</t>
+          <t>2018-02-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,12 +918,7 @@
         <v>57642094</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R4" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1060,32 +1041,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59028932</v>
+        <v>61906545</v>
       </c>
       <c r="B5" t="n">
-        <v>58163</v>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1097,7 +1078,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1136,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-10-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-10-25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,15 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61906545</v>
+        <v>131862902</v>
       </c>
       <c r="B6" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,16 +1170,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1217,22 +1193,27 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R6" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,22 +1240,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-10-25</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-10-25</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>samtidigt med den andra sparvugglan.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,15 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67887187</v>
+        <v>58297330</v>
       </c>
       <c r="B7" t="n">
-        <v>96375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,45 +1298,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6010645</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol × grönvit nattviol</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia × chlorantha</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R7" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,22 +1363,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2016-04-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-07-06</t>
+          <t>2016-04-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,15 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>59222699</v>
+        <v>59028932</v>
       </c>
       <c r="B8" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,33 +1416,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1475,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R8" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,22 +1481,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,56 +1516,51 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Leif Johansson, Leif Edberg, Sören Björklind</t>
+          <t>Leif Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69417872</v>
+        <v>59222703</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1598,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R9" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1628,22 +1599,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-02-07</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-02-07</t>
+          <t>2016-05-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,22 +1634,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Leif Johansson</t>
+          <t>Leif Johansson, Leif Edberg, Sören Björklind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59222703</v>
+        <v>59222699</v>
       </c>
       <c r="B10" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,21 +1652,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1712,7 +1678,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>parning/parningsceremonier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1721,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R10" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1793,55 +1759,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97070575</v>
+        <v>97264590</v>
       </c>
       <c r="B11" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1849,10 +1806,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R11" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1879,22 +1836,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ca, i alar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1903,7 +1865,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1922,15 +1883,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104725820</v>
+        <v>55694725</v>
       </c>
       <c r="B12" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,19 +1894,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1963,21 +1923,20 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540002.8732813115</v>
+        <v>540003</v>
       </c>
       <c r="R12" t="n">
-        <v>6631018.469305436</v>
+        <v>6631018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2004,22 +1963,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,7 +1977,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2047,10 +1995,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56918206</v>
+        <v>55694656</v>
       </c>
       <c r="B13" t="n">
-        <v>56856</v>
+        <v>99156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,39 +2006,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100045</v>
+        <v>219875</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
@@ -2127,22 +2075,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-02-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2015-07-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-02-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2015-07-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2169,50 +2107,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131862902</v>
+        <v>97070575</v>
       </c>
       <c r="B14" t="n">
-        <v>57789</v>
+        <v>110078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2250,27 +2188,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>samtidigt med den andra sparvugglan.</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2279,6 +2202,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2294,6 +2218,224 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104725800</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>540003</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6631018</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>67887187</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99161</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6010645</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nattviol × grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia × chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Folkhögskolebäcken, Skinnskattebergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>540003</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6631018</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-07-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-07-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
